--- a/Revision/20260609/0609_shap_forest_plot_data.xlsx
+++ b/Revision/20260609/0609_shap_forest_plot_data.xlsx
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.09001592546701431</v>
+        <v>0.09948134372029685</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08849704638123512</v>
+        <v>0.09780295826190551</v>
       </c>
       <c r="E2" t="n">
-        <v>0.09148309417068959</v>
+        <v>0.1011030205989624</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -525,10 +525,10 @@
         <v>0.0994816531949012</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09780305463945066</v>
+        <v>0.09780326251525272</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1011031037037994</v>
+        <v>0.1011033351184102</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -562,13 +562,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.06261607259511948</v>
+        <v>0.08739068207767704</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0610458392649889</v>
+        <v>0.08519924515322896</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06415621060878038</v>
+        <v>0.08954018996231201</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -582,10 +582,10 @@
         <v>0.0873907493672057</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08519923748033323</v>
+        <v>0.0851993107553837</v>
       </c>
       <c r="J3" t="n">
-        <v>0.08954025842397839</v>
+        <v>0.08954025890692985</v>
       </c>
       <c r="K3" t="n">
         <v>2</v>
@@ -619,13 +619,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.04961096867918968</v>
+        <v>0.06519819440832111</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04832377377897501</v>
+        <v>0.06350638484459906</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05083697261288762</v>
+        <v>0.0668093036820426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -639,10 +639,10 @@
         <v>0.06519801945346609</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06350640648200236</v>
+        <v>0.06350621442959824</v>
       </c>
       <c r="J4" t="n">
-        <v>0.06680921613934725</v>
+        <v>0.06680912440388703</v>
       </c>
       <c r="K4" t="n">
         <v>3</v>
@@ -676,13 +676,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03125407919287682</v>
+        <v>0.04396452666497754</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03049345873296261</v>
+        <v>0.04289466647025542</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03204029053449631</v>
+        <v>0.04507047265604619</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -696,10 +696,10 @@
         <v>0.0439645521853179</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04289460103760531</v>
+        <v>0.04289469136956791</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04507050156696523</v>
+        <v>0.04507049881836134</v>
       </c>
       <c r="K5" t="n">
         <v>4</v>
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.01463050302118063</v>
+        <v>0.01667835197950725</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01409538530278951</v>
+        <v>0.01606836497398448</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01516427621245384</v>
+        <v>0.01728683130545255</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -753,10 +753,10 @@
         <v>0.0166783481189878</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01606832947649513</v>
+        <v>0.01606836125465804</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01728683403965298</v>
+        <v>0.01728682730408908</v>
       </c>
       <c r="K6" t="n">
         <v>5</v>
@@ -790,13 +790,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01083928998559713</v>
+        <v>0.008861561799764607</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01064326774794608</v>
+        <v>0.008701315483584189</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01103269839659333</v>
+        <v>0.009019666030476397</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -810,10 +810,10 @@
         <v>0.008861556583820899</v>
       </c>
       <c r="I7" t="n">
-        <v>0.008701300501278581</v>
+        <v>0.008701310361961976</v>
       </c>
       <c r="J7" t="n">
-        <v>0.009019675757688105</v>
+        <v>0.00901966072147203</v>
       </c>
       <c r="K7" t="n">
         <v>6</v>
@@ -847,13 +847,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.007904841564595699</v>
+        <v>0.008046728629395436</v>
       </c>
       <c r="D8" t="n">
-        <v>0.007714461430441588</v>
+        <v>0.007852929772497604</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008096066629514098</v>
+        <v>0.008241363254000727</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -867,10 +867,10 @@
         <v>0.0080467241748538</v>
       </c>
       <c r="I8" t="n">
-        <v>0.007852926941172223</v>
+        <v>0.007852925425239948</v>
       </c>
       <c r="J8" t="n">
-        <v>0.008241381504813274</v>
+        <v>0.008241358691712442</v>
       </c>
       <c r="K8" t="n">
         <v>7</v>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.00854389276355505</v>
+        <v>0.006663040420696862</v>
       </c>
       <c r="D9" t="n">
-        <v>0.008312608627602459</v>
+        <v>0.006482681123379112</v>
       </c>
       <c r="E9" t="n">
-        <v>0.008781907381489873</v>
+        <v>0.006848673237392457</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         <v>0.0066630622176575</v>
       </c>
       <c r="I9" t="n">
-        <v>0.006482692375659618</v>
+        <v>0.006482702330326144</v>
       </c>
       <c r="J9" t="n">
-        <v>0.006848680910670194</v>
+        <v>0.006848695641618088</v>
       </c>
       <c r="K9" t="n">
         <v>8</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.00608260091394186</v>
+        <v>0.004744801161570464</v>
       </c>
       <c r="D10" t="n">
-        <v>0.005932335485704243</v>
+        <v>0.004627579692756351</v>
       </c>
       <c r="E10" t="n">
-        <v>0.006232631043531001</v>
+        <v>0.004861822433772899</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
         <v>0.0047447981507591</v>
       </c>
       <c r="I10" t="n">
-        <v>0.004627581990088316</v>
+        <v>0.004627576756327815</v>
       </c>
       <c r="J10" t="n">
-        <v>0.00486183076419278</v>
+        <v>0.004861819348705741</v>
       </c>
       <c r="K10" t="n">
         <v>9</v>
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.005286972038447857</v>
+        <v>0.004159927084886573</v>
       </c>
       <c r="D11" t="n">
-        <v>0.004963823209982366</v>
+        <v>0.003905672163319999</v>
       </c>
       <c r="E11" t="n">
-        <v>0.005596552579663694</v>
+        <v>0.00440351946232184</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1038,10 +1038,10 @@
         <v>0.0041599318354061</v>
       </c>
       <c r="I11" t="n">
-        <v>0.00390566964348756</v>
+        <v>0.003905676623487569</v>
       </c>
       <c r="J11" t="n">
-        <v>0.004403518133888604</v>
+        <v>0.004403524491016999</v>
       </c>
       <c r="K11" t="n">
         <v>10</v>
@@ -1075,13 +1075,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.004300067666918039</v>
+        <v>0.003112859520612042</v>
       </c>
       <c r="D12" t="n">
-        <v>0.004108088905923069</v>
+        <v>0.002973887561233996</v>
       </c>
       <c r="E12" t="n">
-        <v>0.004488848417531699</v>
+        <v>0.00324951960295416</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1095,10 +1095,10 @@
         <v>0.0031128638480843</v>
       </c>
       <c r="I12" t="n">
-        <v>0.002973888420023286</v>
+        <v>0.002973891695508555</v>
       </c>
       <c r="J12" t="n">
-        <v>0.003249524203064402</v>
+        <v>0.003249524120410165</v>
       </c>
       <c r="K12" t="n">
         <v>11</v>
@@ -1132,13 +1132,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.004868174903094769</v>
+        <v>0.002431723216470863</v>
       </c>
       <c r="D13" t="n">
-        <v>0.004755834152456373</v>
+        <v>0.002375611290313036</v>
       </c>
       <c r="E13" t="n">
-        <v>0.004975281760562211</v>
+        <v>0.002485223189062438</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1152,10 +1152,10 @@
         <v>0.0024317262693436</v>
       </c>
       <c r="I13" t="n">
-        <v>0.002375610381997091</v>
+        <v>0.002375614272740844</v>
       </c>
       <c r="J13" t="n">
-        <v>0.002485227748669013</v>
+        <v>0.002485226309100964</v>
       </c>
       <c r="K13" t="n">
         <v>12</v>
@@ -1189,13 +1189,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.002892741933465004</v>
+        <v>0.001527332722829474</v>
       </c>
       <c r="D14" t="n">
-        <v>0.002827138127759099</v>
+        <v>0.001492695832364902</v>
       </c>
       <c r="E14" t="n">
-        <v>0.002953336085192859</v>
+        <v>0.001559326030638549</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1209,10 +1209,10 @@
         <v>0.0015273322983005</v>
       </c>
       <c r="I14" t="n">
-        <v>0.001492694292681368</v>
+        <v>0.001492695417463407</v>
       </c>
       <c r="J14" t="n">
-        <v>0.001559325267998706</v>
+        <v>0.001559325597216892</v>
       </c>
       <c r="K14" t="n">
         <v>13</v>
@@ -1246,13 +1246,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.002130053006112576</v>
+        <v>0.001168371355745274</v>
       </c>
       <c r="D15" t="n">
-        <v>0.002047081181081012</v>
+        <v>0.001122860335565189</v>
       </c>
       <c r="E15" t="n">
-        <v>0.002219380403403193</v>
+        <v>0.001217372276940678</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1266,10 +1266,10 @@
         <v>0.0011683749164679</v>
       </c>
       <c r="I15" t="n">
-        <v>0.001122863279498187</v>
+        <v>0.00112286375758866</v>
       </c>
       <c r="J15" t="n">
-        <v>0.001217372706686367</v>
+        <v>0.001217375986998263</v>
       </c>
       <c r="K15" t="n">
         <v>14</v>
@@ -1303,13 +1303,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.000853903591632843</v>
+        <v>0.0006837702835312223</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0008262482850113883</v>
+        <v>0.0006616265756422425</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0008808526850771159</v>
+        <v>0.0007053508695348619</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1323,10 +1323,10 @@
         <v>0.0006837702833292</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0006616250704159386</v>
+        <v>0.0006616265754467627</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0007053499902661615</v>
+        <v>0.0007053508693264636</v>
       </c>
       <c r="K16" t="n">
         <v>15</v>
@@ -1360,13 +1360,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.001327063306234777</v>
+        <v>0.0006777308685093188</v>
       </c>
       <c r="D17" t="n">
-        <v>0.001267092651687562</v>
+        <v>0.0006471028842431295</v>
       </c>
       <c r="E17" t="n">
-        <v>0.00138976076268591</v>
+        <v>0.000709748552154819</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1380,10 +1380,10 @@
         <v>0.000677729404066</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0006471024733259369</v>
+        <v>0.0006471014859808702</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0007097489087855154</v>
+        <v>0.0007097470185275733</v>
       </c>
       <c r="K17" t="n">
         <v>16</v>
@@ -1531,13 +1531,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0003955873544327915</v>
+        <v>0.000547842106069685</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0003462339998804964</v>
+        <v>0.0004794935957037614</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0004490852123126388</v>
+        <v>0.0006219312439699635</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1551,10 +1551,10 @@
         <v>0.0005478428737097</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0004794941682160398</v>
+        <v>0.0004794942675733875</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0006219312384407521</v>
+        <v>0.0006219321154241729</v>
       </c>
       <c r="K20" t="n">
         <v>19</v>
@@ -1930,13 +1930,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8.318836626131088e-05</v>
+        <v>0.0004197267653280628</v>
       </c>
       <c r="D27" t="n">
-        <v>7.457264455297263e-05</v>
+        <v>0.0003762566164985157</v>
       </c>
       <c r="E27" t="n">
-        <v>9.218472605425632e-05</v>
+        <v>0.0004651184621387841</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1950,10 +1950,10 @@
         <v>0.000419727456247</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0003762567749619089</v>
+        <v>0.0003762572358605461</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0004651186495241292</v>
+        <v>0.0004651192277777189</v>
       </c>
       <c r="K27" t="n">
         <v>26</v>
@@ -1987,13 +1987,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0002497367968317121</v>
+        <v>0.0003941428941886419</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0002197295656515053</v>
+        <v>0.0003467839384052663</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0002810352889355272</v>
+        <v>0.0004435383583651281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2007,10 +2007,10 @@
         <v>0.0003941421175611</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0003467838035699022</v>
+        <v>0.0003467832550948182</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0004435383383454157</v>
+        <v>0.0004435374844077131</v>
       </c>
       <c r="K28" t="n">
         <v>27</v>
